--- a/artfynd/A 51065-2024 artfynd.xlsx
+++ b/artfynd/A 51065-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121238140</v>
+        <v>121237892</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565534</v>
+        <v>565551</v>
       </c>
       <c r="R3" t="n">
-        <v>6949071</v>
+        <v>6949020</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>121237808</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121238527</v>
+        <v>121238433</v>
       </c>
       <c r="B5" t="n">
-        <v>56552</v>
+        <v>90715</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,42 +1015,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565557</v>
+        <v>565493</v>
       </c>
       <c r="R5" t="n">
-        <v>6949090</v>
+        <v>6949118</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121237892</v>
+        <v>121238527</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>56555</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,37 +1117,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565551</v>
+        <v>565557</v>
       </c>
       <c r="R6" t="n">
-        <v>6949020</v>
+        <v>6949090</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121238117</v>
+        <v>121237723</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,25 +1220,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565533</v>
+        <v>565528</v>
       </c>
       <c r="R7" t="n">
-        <v>6949071</v>
+        <v>6948986</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1310,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121237723</v>
+        <v>121238117</v>
       </c>
       <c r="B8" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,25 +1322,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565528</v>
+        <v>565533</v>
       </c>
       <c r="R8" t="n">
-        <v>6948986</v>
+        <v>6949071</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121238433</v>
+        <v>121238140</v>
       </c>
       <c r="B9" t="n">
-        <v>90705</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,25 +1424,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565493</v>
+        <v>565534</v>
       </c>
       <c r="R9" t="n">
-        <v>6949118</v>
+        <v>6949071</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 51065-2024 artfynd.xlsx
+++ b/artfynd/A 51065-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121237892</v>
+        <v>121238140</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565551</v>
+        <v>565534</v>
       </c>
       <c r="R3" t="n">
-        <v>6949020</v>
+        <v>6949071</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121237808</v>
+        <v>121237723</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565538</v>
+        <v>565528</v>
       </c>
       <c r="R4" t="n">
-        <v>6949025</v>
+        <v>6948986</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121238433</v>
+        <v>121238117</v>
       </c>
       <c r="B5" t="n">
-        <v>90715</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565493</v>
+        <v>565533</v>
       </c>
       <c r="R5" t="n">
-        <v>6949118</v>
+        <v>6949071</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121238527</v>
+        <v>121238433</v>
       </c>
       <c r="B6" t="n">
-        <v>56555</v>
+        <v>90715</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,42 +1117,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565557</v>
+        <v>565493</v>
       </c>
       <c r="R6" t="n">
-        <v>6949090</v>
+        <v>6949118</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121237723</v>
+        <v>121237808</v>
       </c>
       <c r="B7" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565528</v>
+        <v>565538</v>
       </c>
       <c r="R7" t="n">
-        <v>6948986</v>
+        <v>6949025</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1310,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238117</v>
+        <v>121238527</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>56555</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,41 +1317,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565533</v>
+        <v>565557</v>
       </c>
       <c r="R8" t="n">
-        <v>6949071</v>
+        <v>6949090</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121238140</v>
+        <v>121237892</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,25 +1424,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565534</v>
+        <v>565551</v>
       </c>
       <c r="R9" t="n">
-        <v>6949071</v>
+        <v>6949020</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 51065-2024 artfynd.xlsx
+++ b/artfynd/A 51065-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121238140</v>
+        <v>121237723</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565534</v>
+        <v>565528</v>
       </c>
       <c r="R3" t="n">
-        <v>6949071</v>
+        <v>6948986</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121237723</v>
+        <v>121237892</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565528</v>
+        <v>565551</v>
       </c>
       <c r="R4" t="n">
-        <v>6948986</v>
+        <v>6949020</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121238117</v>
+        <v>121238527</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>56555</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,41 +1011,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565533</v>
+        <v>565557</v>
       </c>
       <c r="R5" t="n">
-        <v>6949071</v>
+        <v>6949090</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121238433</v>
+        <v>121238117</v>
       </c>
       <c r="B6" t="n">
-        <v>90715</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,25 +1118,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565493</v>
+        <v>565533</v>
       </c>
       <c r="R6" t="n">
-        <v>6949118</v>
+        <v>6949071</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1203,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121237808</v>
+        <v>121238433</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>90727</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565538</v>
+        <v>565493</v>
       </c>
       <c r="R7" t="n">
-        <v>6949025</v>
+        <v>6949118</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1305,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238527</v>
+        <v>121237808</v>
       </c>
       <c r="B8" t="n">
-        <v>56555</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,42 +1326,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565557</v>
+        <v>565538</v>
       </c>
       <c r="R8" t="n">
-        <v>6949090</v>
+        <v>6949025</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121237892</v>
+        <v>121238140</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,25 +1424,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565551</v>
+        <v>565534</v>
       </c>
       <c r="R9" t="n">
-        <v>6949020</v>
+        <v>6949071</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 51065-2024 artfynd.xlsx
+++ b/artfynd/A 51065-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121237723</v>
+        <v>121238527</v>
       </c>
       <c r="B3" t="n">
-        <v>79685</v>
+        <v>56555</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,37 +811,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565528</v>
+        <v>565557</v>
       </c>
       <c r="R3" t="n">
-        <v>6948986</v>
+        <v>6949090</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -999,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121238527</v>
+        <v>121238140</v>
       </c>
       <c r="B5" t="n">
-        <v>56555</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,46 +1016,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565557</v>
+        <v>565534</v>
       </c>
       <c r="R5" t="n">
-        <v>6949090</v>
+        <v>6949071</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121238117</v>
+        <v>121237808</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,25 +1118,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565533</v>
+        <v>565538</v>
       </c>
       <c r="R6" t="n">
-        <v>6949071</v>
+        <v>6949025</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1211,7 +1211,7 @@
         <v>121238433</v>
       </c>
       <c r="B7" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1310,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121237808</v>
+        <v>121238117</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,25 +1322,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565538</v>
+        <v>565533</v>
       </c>
       <c r="R8" t="n">
-        <v>6949025</v>
+        <v>6949071</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121238140</v>
+        <v>121237723</v>
       </c>
       <c r="B9" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,25 +1424,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565534</v>
+        <v>565528</v>
       </c>
       <c r="R9" t="n">
-        <v>6949071</v>
+        <v>6948986</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 51065-2024 artfynd.xlsx
+++ b/artfynd/A 51065-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121238527</v>
+        <v>121238117</v>
       </c>
       <c r="B3" t="n">
-        <v>56555</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,46 +807,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565557</v>
+        <v>565533</v>
       </c>
       <c r="R3" t="n">
-        <v>6949090</v>
+        <v>6949071</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121237892</v>
+        <v>121237723</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565551</v>
+        <v>565528</v>
       </c>
       <c r="R4" t="n">
-        <v>6949020</v>
+        <v>6948986</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121238140</v>
+        <v>121237892</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565534</v>
+        <v>565551</v>
       </c>
       <c r="R5" t="n">
-        <v>6949071</v>
+        <v>6949020</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,7 +1104,7 @@
         <v>121237808</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,7 +1206,7 @@
         <v>121238433</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>90731</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1310,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238117</v>
+        <v>121238527</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>56558</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,41 +1317,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565533</v>
+        <v>565557</v>
       </c>
       <c r="R8" t="n">
-        <v>6949071</v>
+        <v>6949090</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121237723</v>
+        <v>121238140</v>
       </c>
       <c r="B9" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,25 +1424,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565528</v>
+        <v>565534</v>
       </c>
       <c r="R9" t="n">
-        <v>6948986</v>
+        <v>6949071</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 51065-2024 artfynd.xlsx
+++ b/artfynd/A 51065-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121238117</v>
+        <v>121237892</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565533</v>
+        <v>565551</v>
       </c>
       <c r="R3" t="n">
-        <v>6949071</v>
+        <v>6949020</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121237723</v>
+        <v>121238527</v>
       </c>
       <c r="B4" t="n">
-        <v>79688</v>
+        <v>56558</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,37 +913,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565528</v>
+        <v>565557</v>
       </c>
       <c r="R4" t="n">
-        <v>6948986</v>
+        <v>6949090</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121237892</v>
+        <v>121238117</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1016,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,13 +1044,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565551</v>
+        <v>565533</v>
       </c>
       <c r="R5" t="n">
-        <v>6949020</v>
+        <v>6949071</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121237808</v>
+        <v>121237723</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1122,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565538</v>
+        <v>565528</v>
       </c>
       <c r="R6" t="n">
-        <v>6949025</v>
+        <v>6948986</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1305,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238527</v>
+        <v>121238140</v>
       </c>
       <c r="B8" t="n">
-        <v>56558</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,46 +1322,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565557</v>
+        <v>565534</v>
       </c>
       <c r="R8" t="n">
-        <v>6949090</v>
+        <v>6949071</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121238140</v>
+        <v>121237808</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,25 +1424,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565534</v>
+        <v>565538</v>
       </c>
       <c r="R9" t="n">
-        <v>6949071</v>
+        <v>6949025</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 51065-2024 artfynd.xlsx
+++ b/artfynd/A 51065-2024 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121237723</v>
+        <v>121238433</v>
       </c>
       <c r="B6" t="n">
-        <v>79688</v>
+        <v>90731</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,21 +1122,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565528</v>
+        <v>565493</v>
       </c>
       <c r="R6" t="n">
-        <v>6948986</v>
+        <v>6949118</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121238433</v>
+        <v>121237723</v>
       </c>
       <c r="B7" t="n">
-        <v>90731</v>
+        <v>79688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565493</v>
+        <v>565528</v>
       </c>
       <c r="R7" t="n">
-        <v>6949118</v>
+        <v>6948986</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 51065-2024 artfynd.xlsx
+++ b/artfynd/A 51065-2024 artfynd.xlsx
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121238433</v>
+        <v>121237723</v>
       </c>
       <c r="B6" t="n">
-        <v>90731</v>
+        <v>79688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,21 +1122,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565493</v>
+        <v>565528</v>
       </c>
       <c r="R6" t="n">
-        <v>6949118</v>
+        <v>6948986</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121237723</v>
+        <v>121238433</v>
       </c>
       <c r="B7" t="n">
-        <v>79688</v>
+        <v>90731</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,21 +1224,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565528</v>
+        <v>565493</v>
       </c>
       <c r="R7" t="n">
-        <v>6948986</v>
+        <v>6949118</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 51065-2024 artfynd.xlsx
+++ b/artfynd/A 51065-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121237892</v>
+        <v>121238117</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565551</v>
+        <v>565533</v>
       </c>
       <c r="R3" t="n">
-        <v>6949020</v>
+        <v>6949071</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121238527</v>
+        <v>121237892</v>
       </c>
       <c r="B4" t="n">
-        <v>56558</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,42 +913,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565557</v>
+        <v>565551</v>
       </c>
       <c r="R4" t="n">
-        <v>6949090</v>
+        <v>6949020</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121238117</v>
+        <v>121238140</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,7 +1039,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565533</v>
+        <v>565534</v>
       </c>
       <c r="R5" t="n">
         <v>6949071</v>
@@ -1106,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121237723</v>
+        <v>121237808</v>
       </c>
       <c r="B6" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565528</v>
+        <v>565538</v>
       </c>
       <c r="R6" t="n">
-        <v>6948986</v>
+        <v>6949025</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1211,7 +1206,7 @@
         <v>121238433</v>
       </c>
       <c r="B7" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1310,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238140</v>
+        <v>121237723</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565534</v>
+        <v>565528</v>
       </c>
       <c r="R8" t="n">
-        <v>6949071</v>
+        <v>6948986</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1412,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121237808</v>
+        <v>121238527</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>56559</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,37 +1423,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565538</v>
+        <v>565557</v>
       </c>
       <c r="R9" t="n">
-        <v>6949025</v>
+        <v>6949090</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 51065-2024 artfynd.xlsx
+++ b/artfynd/A 51065-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121238117</v>
+        <v>121238527</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>56560</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,41 +807,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565533</v>
+        <v>565557</v>
       </c>
       <c r="R3" t="n">
-        <v>6949071</v>
+        <v>6949090</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121237892</v>
+        <v>121238117</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +914,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,13 +942,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565551</v>
+        <v>565533</v>
       </c>
       <c r="R4" t="n">
-        <v>6949020</v>
+        <v>6949071</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121238140</v>
+        <v>121237808</v>
       </c>
       <c r="B5" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1016,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565534</v>
+        <v>565538</v>
       </c>
       <c r="R5" t="n">
-        <v>6949071</v>
+        <v>6949025</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1101,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121237808</v>
+        <v>121237892</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,13 +1146,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565538</v>
+        <v>565551</v>
       </c>
       <c r="R6" t="n">
-        <v>6949025</v>
+        <v>6949020</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121238433</v>
+        <v>121238140</v>
       </c>
       <c r="B7" t="n">
-        <v>90737</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1220,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565493</v>
+        <v>565534</v>
       </c>
       <c r="R7" t="n">
-        <v>6949118</v>
+        <v>6949071</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1308,7 +1313,7 @@
         <v>121237723</v>
       </c>
       <c r="B8" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121238527</v>
+        <v>121238433</v>
       </c>
       <c r="B9" t="n">
-        <v>56559</v>
+        <v>90738</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,42 +1428,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565557</v>
+        <v>565493</v>
       </c>
       <c r="R9" t="n">
-        <v>6949090</v>
+        <v>6949118</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 51065-2024 artfynd.xlsx
+++ b/artfynd/A 51065-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121238527</v>
+        <v>121238433</v>
       </c>
       <c r="B3" t="n">
-        <v>56560</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,42 +811,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565557</v>
+        <v>565493</v>
       </c>
       <c r="R3" t="n">
-        <v>6949090</v>
+        <v>6949118</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121238117</v>
+        <v>121237808</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565533</v>
+        <v>565538</v>
       </c>
       <c r="R4" t="n">
-        <v>6949071</v>
+        <v>6949025</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1004,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121237808</v>
+        <v>121237892</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1044,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565538</v>
+        <v>565551</v>
       </c>
       <c r="R5" t="n">
-        <v>6949025</v>
+        <v>6949020</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121237892</v>
+        <v>121237723</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,13 +1141,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565551</v>
+        <v>565528</v>
       </c>
       <c r="R6" t="n">
-        <v>6949020</v>
+        <v>6948986</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1310,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121237723</v>
+        <v>121238117</v>
       </c>
       <c r="B8" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565528</v>
+        <v>565533</v>
       </c>
       <c r="R8" t="n">
-        <v>6948986</v>
+        <v>6949071</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1412,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121238433</v>
+        <v>121238527</v>
       </c>
       <c r="B9" t="n">
-        <v>90738</v>
+        <v>56560</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,37 +1423,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565493</v>
+        <v>565557</v>
       </c>
       <c r="R9" t="n">
-        <v>6949118</v>
+        <v>6949090</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 51065-2024 artfynd.xlsx
+++ b/artfynd/A 51065-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121238433</v>
+        <v>121237808</v>
       </c>
       <c r="B3" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565493</v>
+        <v>565538</v>
       </c>
       <c r="R3" t="n">
-        <v>6949118</v>
+        <v>6949025</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121237808</v>
+        <v>121238433</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565538</v>
+        <v>565493</v>
       </c>
       <c r="R4" t="n">
-        <v>6949025</v>
+        <v>6949118</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121237892</v>
+        <v>121238140</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565551</v>
+        <v>565534</v>
       </c>
       <c r="R5" t="n">
-        <v>6949020</v>
+        <v>6949071</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121238140</v>
+        <v>121238117</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565534</v>
+        <v>565533</v>
       </c>
       <c r="R7" t="n">
         <v>6949071</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121238117</v>
+        <v>121237892</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565533</v>
+        <v>565551</v>
       </c>
       <c r="R8" t="n">
-        <v>6949071</v>
+        <v>6949020</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 51065-2024 artfynd.xlsx
+++ b/artfynd/A 51065-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121237808</v>
+        <v>121238527</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>56560</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,37 +811,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565538</v>
+        <v>565557</v>
       </c>
       <c r="R3" t="n">
-        <v>6949025</v>
+        <v>6949090</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -999,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121238140</v>
+        <v>121237892</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1016,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,13 +1044,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565534</v>
+        <v>565551</v>
       </c>
       <c r="R5" t="n">
-        <v>6949071</v>
+        <v>6949020</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121237723</v>
+        <v>121237808</v>
       </c>
       <c r="B6" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1122,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565528</v>
+        <v>565538</v>
       </c>
       <c r="R6" t="n">
-        <v>6948986</v>
+        <v>6949025</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1203,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121238117</v>
+        <v>121237723</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1220,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565533</v>
+        <v>565528</v>
       </c>
       <c r="R7" t="n">
-        <v>6949071</v>
+        <v>6948986</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1305,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121237892</v>
+        <v>121238117</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1322,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,13 +1350,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565551</v>
+        <v>565533</v>
       </c>
       <c r="R8" t="n">
-        <v>6949020</v>
+        <v>6949071</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121238527</v>
+        <v>121238140</v>
       </c>
       <c r="B9" t="n">
-        <v>56560</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,46 +1424,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kilen, Kilen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565557</v>
+        <v>565534</v>
       </c>
       <c r="R9" t="n">
-        <v>6949090</v>
+        <v>6949071</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 51065-2024 artfynd.xlsx
+++ b/artfynd/A 51065-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121237808</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121237892</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121237723</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76621781</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121238527</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1277,6 +1307,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121238117</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1374,8 +1409,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121238140</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>